--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -519,7 +519,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -521,10 +521,102 @@
       <c r="A11" t="str">
         <v>35</v>
       </c>
+      <c r="C11" t="str">
+        <v>211_海洋之心_Nautica_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F11" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F12" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="str">
+        <v>284_可爱瓷_undefined_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F13" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F14" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>36</v>
+      </c>
+      <c r="C15" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F15" t="str">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F16" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>37</v>
+      </c>
+      <c r="C17" t="str">
+        <v>195_闺蜜_Alter Ego_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F17" t="str">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="str">
+        <v>279_完美甜蜜_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F18" t="str">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F19" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>38</v>
+      </c>
+      <c r="C20" t="str">
+        <v>594_绿毛球_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F20" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -579,7 +671,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202020161420309200</v>
+        <v>02020201614203092020514103610252410400</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -613,6 +613,9 @@
       <c r="A21" t="str">
         <v>39</v>
       </c>
+      <c r="C21" t="str">
+        <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -616,6 +616,9 @@
       <c r="C21" t="str">
         <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
       </c>
+      <c r="F21" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -674,7 +677,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02020201614203092020514103610252410400</v>
+        <v>02020201614203092020514103610252410401</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -617,7 +617,7 @@
         <v>629_干花蓬莱松_undefined_undefined_1bunch</v>
       </c>
       <c r="F21" t="str">
-        <v>1</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -677,7 +677,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>02020201614203092020514103610252410401</v>
+        <v>0202020161420309202051410361025241040110</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -620,9 +620,101 @@
         <v>110</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>41</v>
+      </c>
+      <c r="C22" t="str">
+        <v>152_白荔枝_White Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F22" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="str">
+        <v>160_卡布奇诺_Cappuccino_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F23" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F24" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>42</v>
+      </c>
+      <c r="C25" t="str">
+        <v>170_奶油杯_Butter Cup_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F25" t="str">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F26" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>43</v>
+      </c>
+      <c r="C27" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F27" t="str">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>44</v>
+      </c>
+      <c r="C28" t="str">
+        <v>192_粉荔枝_Pink Ohara_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F28" t="str">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>54</v>
+      </c>
+      <c r="C29" t="str">
+        <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F29" t="str">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F30" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -677,7 +769,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202020161420309202051410361025241040110</v>
+        <v>0202020161420309202051410361025241040110229926134146100290</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -690,7 +690,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="C29" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -690,7 +690,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C29" t="str">
         <v>106_绣球粉_Hydrangea Pink S_Hydrangea L._1stem</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>55</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -709,7 +709,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>4</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -711,6 +711,9 @@
       <c r="A31" t="str">
         <v>46</v>
       </c>
+      <c r="C31" t="str">
+        <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -714,6 +714,9 @@
       <c r="C31" t="str">
         <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
       </c>
+      <c r="F31" t="str">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -772,7 +775,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202020161420309202051410361025241040110229926134146100290</v>
+        <v>0202020161420309202051410361025241040110229926134146100298</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L41"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -715,12 +715,101 @@
         <v>125_绣球蓝_Hydrangea Light Blue S_Hydrangea L._1stem</v>
       </c>
       <c r="F31" t="str">
-        <v>8</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="str">
+        <v>506_紫罗兰香槟色_violet champagne_undefined_1bunch</v>
+      </c>
+      <c r="F32" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="str">
+        <v>505_紫罗兰紫_violet purple_undefined_1bunch</v>
+      </c>
+      <c r="F33" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="str">
+        <v>423_鼠尾紫色_veronica purple_undefined_1bunch</v>
+      </c>
+      <c r="F34" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="str">
+        <v>518_多头鼠尾 紫色_spray veronica purple_undefined_1bunch</v>
+      </c>
+      <c r="F35" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>47</v>
+      </c>
+      <c r="C36" t="str">
+        <v>238_苏菲宝贝_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F36" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>48</v>
+      </c>
+      <c r="C37" t="str">
+        <v>595_玉兰叶_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F37" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+      <c r="C38" t="str">
+        <v>412_紫罗兰粉_violet pink_undefined_1bunch</v>
+      </c>
+      <c r="F38" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="str">
+        <v>411_紫罗兰白_violet white_undefined_1bunch</v>
+      </c>
+      <c r="F39" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>49</v>
+      </c>
+      <c r="C40" t="str">
+        <v>274_仙子之吻_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F40" t="str">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="str">
+        <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -775,7 +864,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202020161420309202051410361025241040110229926134146100298</v>
+        <v>020202016142030920205141036102524104011022992613414610029851020151560203040300</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -806,6 +806,9 @@
       <c r="C41" t="str">
         <v>229_黄蝴蝶_Yellow Butterfly_Rosa rugosa Thunb._10stems</v>
       </c>
+      <c r="F41" t="str">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -864,7 +867,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>020202016142030920205141036102524104011022992613414610029851020151560203040300</v>
+        <v>0202020161420309202051410361025241040110229926134146100298510201515602030403020</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
+++ b/DateBase/orders/Dang Nguyen 195_2026-10-12.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -810,9 +810,181 @@
         <v>20</v>
       </c>
     </row>
+    <row r="42">
+      <c r="C42" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>50</v>
+      </c>
+      <c r="C43" t="str">
+        <v>246_多头蓝莓_Blueberry Spray_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F43" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F44" t="str">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>51</v>
+      </c>
+      <c r="C45" t="str">
+        <v>147_娜欧米_Red Naomi_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F45" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="str">
+        <v>2_粉洋桔梗_Pink Lisianthus_Eustoma grandiflorum (Raf.) Shinners_800/600g</v>
+      </c>
+      <c r="F46" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="str">
+        <v>424_鼠尾白色_veronica white_undefined_1bunch</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="str">
+        <v>517_鼠尾粉色_veronica pink_undefined_1bunch</v>
+      </c>
+      <c r="F48" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F49" t="str">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>52</v>
+      </c>
+      <c r="C50" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F50" t="str">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>53</v>
+      </c>
+      <c r="C51" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F51" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F52" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>54</v>
+      </c>
+      <c r="C53" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="str">
+        <v>189_洛神_Mandala_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>55</v>
+      </c>
+      <c r="C55" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>56</v>
+      </c>
+      <c r="C56" t="str">
+        <v>144_高原红_High Plateau Red_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="F57" t="str">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>57</v>
+      </c>
+      <c r="C58" t="str">
+        <v>111_绣球紫_Hydrangea Purple&amp;Pink S_Hydrangea L._1stem</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L41"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L58"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -867,7 +1039,10 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0202020161420309202051410361025241040110229926134146100298510201515602030403020</v>
+        <v>02020201614203092020514103610252410401102299261341461002985102015156020304030208104282015152340102982929136535</v>
+      </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
       </c>
     </row>
   </sheetData>
